--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run5/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="497">
   <si>
     <t>Filename</t>
   </si>
@@ -808,691 +808,703 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9986,0.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0298,0.0001,0.0007,0.9903</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9978,0.0000,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0021,0.0044,0.9961</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0000,0.0020</t>
+  </si>
+  <si>
+    <t>0.0250,0.0004,0.0000,0.9930</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9989,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
+    <t>0.9982,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8412,0.0027,0.1295,0.0013</t>
+  </si>
+  <si>
+    <t>0.2377,0.0002,0.8409,0.0002</t>
+  </si>
+  <si>
+    <t>0.0513,0.0010,0.9770,0.0000</t>
+  </si>
+  <si>
+    <t>0.0144,0.0010,0.9852,0.0003</t>
+  </si>
+  <si>
+    <t>0.0242,0.0032,0.9715,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9981,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8350,0.0002,0.1321,0.0029</t>
+  </si>
+  <si>
+    <t>0.1790,0.0003,0.8424,0.0007</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.2914,0.0003,0.7520,0.0003</t>
+  </si>
+  <si>
+    <t>0.9743,0.0001,0.0434,0.0000</t>
+  </si>
+  <si>
+    <t>0.0319,0.0002,0.9771,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9997,0.0025</t>
+  </si>
+  <si>
+    <t>0.9562,0.0431,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.1538,0.0635,0.6928,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0029,0.9985,0.0023</t>
+  </si>
+  <si>
+    <t>0.0070,0.9823,0.0077,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7609,0.0043,0.2082,0.0016</t>
+  </si>
+  <si>
+    <t>0.9719,0.0402,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9973,0.0081,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.7103,0.5784,0.0032</t>
+  </si>
+  <si>
+    <t>0.0018,0.0009,0.9864,0.0084</t>
+  </si>
+  <si>
+    <t>0.0008,0.0056,0.9971,0.0005</t>
+  </si>
+  <si>
+    <t>0.0285,0.0000,0.9582,0.0029</t>
+  </si>
+  <si>
+    <t>0.0006,0.0482,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9933,0.0133,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0446,0.0124,0.0008,0.9664</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9973,0.0179,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0563,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0676,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0375,0.0003,0.9774,0.0000</t>
+  </si>
+  <si>
+    <t>0.0046,0.0001,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0020,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0031</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9603,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0032,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9975,0.0026</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9856,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9977,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5251,0.0093,0.4397,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0024,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9898,0.9928,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9905,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0108,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0005,0.0003,0.9982</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0020,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0003,0.9970,0.0071,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9811,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.8628,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9837,0.9857,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9818,0.9736,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9910,0.9165,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9991,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.7620,0.0009,0.2781,0.0004</t>
-  </si>
-  <si>
-    <t>0.0931,0.0003,0.9189,0.0012</t>
-  </si>
-  <si>
-    <t>0.1911,0.0006,0.8963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0008,0.9966,0.0002</t>
-  </si>
-  <si>
-    <t>0.9572,0.0007,0.0377,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9962,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.3076,0.0001,0.6485,0.0027</t>
-  </si>
-  <si>
-    <t>0.0175,0.0008,0.9776,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0650,0.0001,0.9723,0.0000</t>
-  </si>
-  <si>
-    <t>0.0054,0.0001,0.9957,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0009</t>
-  </si>
-  <si>
-    <t>0.3784,0.7069,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.5040,0.0065,0.4231,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0035,0.9988,0.0022</t>
-  </si>
-  <si>
-    <t>0.0011,0.9982,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0006,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.2069,0.0100,0.7155,0.0038</t>
-  </si>
-  <si>
-    <t>0.3444,0.8055,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.5042,0.8654,0.0015</t>
-  </si>
-  <si>
-    <t>0.0018,0.0011,0.9944,0.0032</t>
-  </si>
-  <si>
-    <t>0.0021,0.0016,0.9954,0.0006</t>
-  </si>
-  <si>
-    <t>0.0061,0.0001,0.9934,0.0010</t>
-  </si>
-  <si>
-    <t>0.0006,0.0063,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0152,0.0104,0.0003,0.9903</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9984,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0107,0.1902,0.8805,0.0002</t>
-  </si>
-  <si>
-    <t>0.0069,0.0005,0.9941,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0022,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9999,0.0007</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0018,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9681,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9990,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9537,0.9022,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9992,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9900,0.0005,0.0077,0.0000</t>
-  </si>
-  <si>
-    <t>0.9928,0.0003,0.0041,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0025,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9808,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9778,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.5719,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0006,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0014,0.9997</t>
-  </si>
-  <si>
-    <t>0.0010,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9978,0.0098,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9623,0.9600,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9783,0.8715,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9884,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9935,0.0927,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0019,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0009,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0007,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.9927,0.0002,0.0046,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9991,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0053,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9752,0.0005,0.0170,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0001,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9762,0.0035,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.0328,0.0013,0.9579,0.0028</t>
+  </si>
+  <si>
+    <t>0.0023,0.0012,0.0002,0.9981</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9934,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9989,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9442,0.0673,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9092,0.0885,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.4442,0.8794,0.0029</t>
+  </si>
+  <si>
+    <t>0.0002,0.0862,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0031,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9711,0.0023,0.0181,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0000,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.8257,0.0343,0.0566,0.0052</t>
+  </si>
+  <si>
+    <t>0.0094,0.0000,0.0000,0.9989</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.1253,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9984,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.1710,0.7664,0.0153,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.0011,0.0004,0.9971</t>
+  </si>
+  <si>
+    <t>0.0006,0.0020,0.9957,0.0151</t>
+  </si>
+  <si>
+    <t>0.9548,0.0000,0.0031,0.0367</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.0328,0.8569,0.1014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9959,0.0004,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0017,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.7801,0.1214,0.0092,0.0009</t>
+  </si>
+  <si>
+    <t>0.9958,0.0006,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9894,0.0069,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0020,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.5622,0.5191,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9507,0.0470,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.9131,0.0968,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9379,0.0390,0.0134,0.0006</t>
+  </si>
+  <si>
+    <t>0.9812,0.0184,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0015,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9435,0.0478,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9895,0.0036,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0101,0.9977,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0021,0.0024,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0001,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8869,0.1988,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6560,0.0013,0.3096,0.0005</t>
-  </si>
-  <si>
-    <t>0.9279,0.0018,0.0489,0.0001</t>
-  </si>
-  <si>
-    <t>0.5038,0.0169,0.3267,0.0004</t>
-  </si>
-  <si>
-    <t>0.9122,0.0001,0.1073,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0233,0.0426,0.8999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0067,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9885,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5352,0.4152,0.0103,0.0001</t>
-  </si>
-  <si>
-    <t>0.8645,0.1545,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.1990,0.9171,0.0034</t>
-  </si>
-  <si>
-    <t>0.0003,0.3480,0.9928,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0073,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.1621,0.0041,0.8553,0.0005</t>
-  </si>
-  <si>
-    <t>0.9951,0.0000,0.0043,0.0000</t>
-  </si>
-  <si>
-    <t>0.8960,0.0162,0.0551,0.0034</t>
-  </si>
-  <si>
-    <t>0.0119,0.0000,0.0008,0.9953</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.6991,0.0000</t>
+    <t>0.0355,0.0104,0.9339,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0129,0.0020,0.9823,0.0007</t>
+  </si>
+  <si>
+    <t>0.0062,0.0015,0.9927,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0008,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0932,0.4039,0.2029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.9715,0.0356,0.0003</t>
+  </si>
+  <si>
+    <t>0.9293,0.0017,0.0699,0.0001</t>
+  </si>
+  <si>
+    <t>0.9871,0.0007,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.7027,0.0459,0.0673,0.0021</t>
+  </si>
+  <si>
+    <t>0.0062,0.9925,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0276,0.9768,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.9369,0.1021,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9636,0.0816,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8644,0.3138,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9909,0.0091,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9833,0.0002,0.0062,0.0013</t>
+  </si>
+  <si>
+    <t>0.9848,0.0003,0.0113,0.0002</t>
+  </si>
+  <si>
+    <t>0.3477,0.0017,0.7472,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0062,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0910,0.9921,0.0007</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0027,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0001,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0108,0.9903,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.6034,0.3750,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0114,0.0006,0.0004,0.9955</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0014,0.9972,0.0025</t>
-  </si>
-  <si>
-    <t>0.9901,0.0002,0.0012,0.0075</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.0023,0.9933,0.0037,0.0004</t>
-  </si>
-  <si>
-    <t>0.9878,0.0025,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0233,0.8078,0.0410,0.0057</t>
-  </si>
-  <si>
-    <t>0.9922,0.0008,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9852,0.0098,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0017,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0013,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.8724,0.1396,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9425,0.0500,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.0273,0.2287,0.8592,0.0004</t>
-  </si>
-  <si>
-    <t>0.9668,0.0381,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9948,0.0013,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9753,0.0073,0.0073,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.9822,0.0041,0.0016,0.0019</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.1401,0.0099,0.8027,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.2935,0.0011,0.7023,0.0008</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0142,0.0019,0.9831,0.0007</t>
-  </si>
-  <si>
-    <t>0.0596,0.5474,0.1527,0.0003</t>
-  </si>
-  <si>
-    <t>0.0980,0.7380,0.0273,0.0002</t>
-  </si>
-  <si>
-    <t>0.9203,0.0039,0.0652,0.0001</t>
-  </si>
-  <si>
-    <t>0.9629,0.0020,0.0195,0.0005</t>
-  </si>
-  <si>
-    <t>0.5669,0.0011,0.4598,0.0004</t>
-  </si>
-  <si>
-    <t>0.0252,0.9811,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0100,0.9879,0.0035,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0037,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9910,0.0173,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9188,0.1848,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9410,0.0406,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0003,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0001,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9864,0.0001,0.0142,0.0001</t>
-  </si>
-  <si>
-    <t>0.0264,0.0019,0.9719,0.0012</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0019,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0093,0.9952,0.0002</t>
-  </si>
-  <si>
-    <t>0.1812,0.0015,0.7791,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0294,0.9652,0.0005</t>
-  </si>
-  <si>
-    <t>0.9954,0.0023,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0006,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0178,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0217,0.5153,0.3251,0.0007</t>
-  </si>
-  <si>
-    <t>0.9839,0.0001,0.0150,0.0010</t>
-  </si>
-  <si>
-    <t>0.1438,0.0004,0.9018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.1319,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0292,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0005,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.9782,0.0004,0.0202,0.0003</t>
-  </si>
-  <si>
-    <t>0.7141,0.0001,0.4115,0.0002</t>
-  </si>
-  <si>
-    <t>0.9924,0.0002,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0000</t>
+    <t>0.0004,0.0279,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.0751,0.9802,0.0002</t>
+  </si>
+  <si>
+    <t>0.8004,0.0005,0.2518,0.0019</t>
+  </si>
+  <si>
+    <t>0.0602,0.0006,0.9649,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0015,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.1549,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0016,0.9969,0.0004</t>
+  </si>
+  <si>
+    <t>0.9868,0.0000,0.0237,0.0000</t>
+  </si>
+  <si>
+    <t>0.2811,0.0001,0.8073,0.0010</t>
+  </si>
+  <si>
+    <t>0.9725,0.0007,0.0226,0.0010</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9940,0.0078,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0054,0.9935,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0062,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0017,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0029,0.0571,0.9287,0.0012</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.2993,0.0004,0.6688,0.0023</t>
-  </si>
-  <si>
-    <t>0.8142,0.0006,0.1367,0.0012</t>
-  </si>
-  <si>
-    <t>0.0017,0.0003,0.9974,0.0005</t>
-  </si>
-  <si>
-    <t>0.7716,0.0001,0.0001,0.5252</t>
-  </si>
-  <si>
-    <t>0.0001,0.0069,0.0006,0.9990</t>
-  </si>
-  <si>
-    <t>0.0070,0.0000,0.0008,0.9969</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0618,0.0068,0.0001,0.9411</t>
+    <t>0.0008,0.0062,0.9964,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0025,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0079,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.0194,0.0224,0.9381,0.0007</t>
+  </si>
+  <si>
+    <t>0.0035,0.0002,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0474,0.0007,0.9535,0.0012</t>
+  </si>
+  <si>
+    <t>0.2298,0.0011,0.7021,0.0020</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9985,0.0017</t>
+  </si>
+  <si>
+    <t>0.0794,0.0000,0.0011,0.9765</t>
+  </si>
+  <si>
+    <t>0.0002,0.0192,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.2255,0.0000,0.0000,0.9655</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9246,0.0040,0.0004,0.0232</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1890,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1892,7 +1904,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1906,7 +1918,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1920,7 +1932,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1934,7 +1946,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1948,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1962,7 +1974,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1976,7 +1988,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1990,7 +2002,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2004,7 +2016,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2018,7 +2030,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2032,7 +2044,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2046,7 +2058,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2060,7 +2072,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2074,7 +2086,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2088,7 +2100,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2099,10 +2111,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2116,7 +2128,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2130,7 +2142,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2144,7 +2156,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2158,7 +2170,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2172,7 +2184,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2183,10 +2195,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2200,7 +2212,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2214,7 +2226,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2228,7 +2240,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2239,10 +2251,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2256,7 +2268,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2270,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,10 +2293,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2295,10 +2307,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2312,7 +2324,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2326,7 +2338,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2340,7 +2352,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,10 +2363,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,10 +2377,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2382,7 +2394,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2396,7 +2408,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2410,7 +2422,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2424,7 +2436,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2438,7 +2450,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2452,7 +2464,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2466,7 +2478,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2480,7 +2492,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2494,7 +2506,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2508,7 +2520,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2522,7 +2534,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2536,7 +2548,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2550,7 +2562,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2564,7 +2576,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2578,7 +2590,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2592,7 +2604,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2606,7 +2618,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2620,7 +2632,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2634,7 +2646,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2648,7 +2660,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2662,7 +2674,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2676,7 +2688,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2690,7 +2702,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2704,7 +2716,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2718,7 +2730,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2732,7 +2744,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2746,7 +2758,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2760,7 +2772,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2774,7 +2786,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2788,7 +2800,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2802,7 +2814,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2816,7 +2828,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2830,7 +2842,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2844,7 +2856,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2858,7 +2870,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2872,7 +2884,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2886,7 +2898,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2900,7 +2912,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2911,10 +2923,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2928,7 +2940,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2942,7 +2954,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2968,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +2982,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +2996,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +3010,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,7 +3024,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3038,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3040,7 +3052,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3054,7 +3066,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3080,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,10 +3091,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3108,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>349</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3110,7 +3122,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3124,7 +3136,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3138,7 +3150,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3164,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3178,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3180,7 +3192,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>322</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3194,7 +3206,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3208,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3222,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3236,7 +3248,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3250,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3264,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3278,7 +3290,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3292,7 +3304,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>355</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3306,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3332,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3334,7 +3346,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3348,7 +3360,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3362,7 +3374,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3376,7 +3388,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3390,7 +3402,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3404,7 +3416,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3418,7 +3430,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3432,7 +3444,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>283</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3446,7 +3458,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3460,7 +3472,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3474,7 +3486,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3488,7 +3500,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3502,7 +3514,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3513,10 +3525,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3530,7 +3542,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3544,7 +3556,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3558,7 +3570,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3572,7 +3584,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>282</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3586,7 +3598,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3612,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3614,7 +3626,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3628,7 +3640,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3654,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3668,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3712,7 +3724,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3726,7 +3738,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3740,7 +3752,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3754,7 +3766,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3768,7 +3780,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3782,7 +3794,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3796,7 +3808,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3810,7 +3822,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3821,10 +3833,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3838,7 +3850,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3852,7 +3864,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3866,7 +3878,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3880,7 +3892,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>391</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3906,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3920,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3919,10 +3931,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3948,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3962,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3976,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3975,10 +3987,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +4004,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4006,7 +4018,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>400</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4046,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4060,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4074,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4076,7 +4088,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4102,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4104,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4115,10 +4127,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,7 +4144,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4146,7 +4158,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4160,7 +4172,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>356</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4258,7 +4270,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4269,10 +4281,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4286,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4300,7 +4312,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,10 +4323,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4328,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4342,7 +4354,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4356,7 +4368,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4370,7 +4382,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4384,7 +4396,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4398,7 +4410,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4412,7 +4424,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>427</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4426,7 +4438,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4440,7 +4452,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4454,7 +4466,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4468,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4510,7 +4522,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4524,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4538,7 +4550,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4549,10 +4561,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4566,7 +4578,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4580,7 +4592,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4594,7 +4606,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4608,7 +4620,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4622,7 +4634,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4636,7 +4648,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4650,7 +4662,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4664,7 +4676,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4678,7 +4690,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4692,7 +4704,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4706,7 +4718,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4720,7 +4732,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4734,7 +4746,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4748,7 +4760,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4762,7 +4774,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4776,7 +4788,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4790,7 +4802,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4804,7 +4816,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4818,7 +4830,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4832,7 +4844,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4846,7 +4858,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4860,7 +4872,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>316</v>
+        <v>460</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4874,7 +4886,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>269</v>
+        <v>461</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4888,7 +4900,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4902,7 +4914,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>268</v>
+        <v>463</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4916,7 +4928,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4930,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4956,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,10 +4967,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +4984,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +4998,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +5012,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,7 +5026,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5042,7 +5054,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5056,7 +5068,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5070,7 +5082,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>286</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,7 +5096,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5098,7 +5110,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5109,10 +5121,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5126,7 +5138,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5140,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5166,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>475</v>
+        <v>357</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5180,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>476</v>
+        <v>357</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5194,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>355</v>
+        <v>480</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5210,7 +5222,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5224,7 +5236,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5238,7 +5250,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>353</v>
+        <v>483</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5252,7 +5264,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5266,7 +5278,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5280,7 +5292,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5294,7 +5306,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5308,7 +5320,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5322,7 +5334,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,10 +5345,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5362,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5364,7 +5376,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5390,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5404,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5418,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5432,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>391</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,10 +5443,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
